--- a/education_surveys/050_university_subject_assessment_form--education_surveys.xlsx
+++ b/education_surveys/050_university_subject_assessment_form--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Course Assessment</t>
+          <t>What's your assessment of the course?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>student_name</t>
+          <t>course_instructor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Student Name</t>
+          <t>Who is your course instructor?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,19 +566,15 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>email_address</t>
+          <t>instructor_feedback</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Email Address</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Your Email Address</t>
-        </is>
-      </c>
+          <t>What did you learn from your instructor?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -593,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>course_name</t>
+          <t>course_rating</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Course Name</t>
+          <t>How would you rate your experience with the course?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -616,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>assessment_rating</t>
+          <t>course_like</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rating</t>
+          <t>What do you like about the course?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -634,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>assessment_comments</t>
+          <t>student_feedback</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>What do you think the course could improve on?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -662,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>submitted_by</t>
+          <t>email_sent_to</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Submitted By</t>
+          <t>Email address to send feedback to</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -685,19 +681,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>email_sent_to</t>
+          <t>course_name</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Email Sent To</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Enter the email address to send feedback to</t>
-        </is>
-      </c>
+          <t>Course Name</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -712,7 +704,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>submitted_time</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -735,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>course_instructor</t>
+          <t>student_feedback_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Course Instructor</t>
+          <t>Student Feedback 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -753,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>course_instructor_multiple</t>
+          <t>student_feedback_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Course Instructor(s)</t>
+          <t>What do you dislike about the course?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -781,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>submitted_by_2</t>
+          <t>course_evaluation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Submitted By</t>
+          <t>How would you evaluate the course?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -804,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>course_name_2</t>
+          <t>assessment_comments</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Course Name</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -827,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>assessment_comments_2</t>
+          <t>student_name</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Your Name</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -845,251 +837,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>submitted_2</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>submitter_2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Student</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>submitted_by_3</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Submitted By</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>course_name_3</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Course Name</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>submitted_3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>submitted_by_4</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Submitted By</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>course_instructor_2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Course Instructor</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>course_instructor_3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Course Instructor</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>submitted_4</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>submitted_by_5</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Submitted By</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submitted_5</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1106,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1134,85 +896,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>course_instructor_multiple_choices</t>
+          <t>course_instructor_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>professor_john</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Professor John</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>course_instructor_multiple_choices</t>
+          <t>course_instructor_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>professor_jane</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>submitter_2_choices</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>student_1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Student 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>submitter_2_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>student_2</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Student 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>submitter_2_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>student_3</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Student 3</t>
+          <t>Professor Jane</t>
         </is>
       </c>
     </row>
